--- a/goDTL.xlsx
+++ b/goDTL.xlsx
@@ -29,58 +29,58 @@
     <t>Ukko-Pekka Luukkonen</t>
   </si>
   <si>
+    <t>Rasmus Dahlin</t>
+  </si>
+  <si>
+    <t>Jason Zucker</t>
+  </si>
+  <si>
+    <t>Mattias Samuelsson</t>
+  </si>
+  <si>
+    <t>Peyton Krebs</t>
+  </si>
+  <si>
+    <t>Josh Norris</t>
+  </si>
+  <si>
+    <t>Bowen Byram</t>
+  </si>
+  <si>
+    <t>Owen Power</t>
+  </si>
+  <si>
+    <t>Tage Thompson</t>
+  </si>
+  <si>
+    <t>Jordan Greenway</t>
+  </si>
+  <si>
     <t>Josh Doan</t>
   </si>
   <si>
-    <t>Rasmus Dahlin</t>
-  </si>
-  <si>
-    <t>Josh Norris</t>
+    <t>Alex Tuch</t>
+  </si>
+  <si>
+    <t>Noah Ostlund</t>
+  </si>
+  <si>
+    <t>Beck Malenstyn</t>
+  </si>
+  <si>
+    <t>Ryan McLeod</t>
+  </si>
+  <si>
+    <t>Zach Metsa</t>
+  </si>
+  <si>
+    <t>Jacob Bryson</t>
   </si>
   <si>
     <t>Zach Benson</t>
   </si>
   <si>
-    <t>Tage Thompson</t>
-  </si>
-  <si>
-    <t>Mattias Samuelsson</t>
-  </si>
-  <si>
-    <t>Alex Tuch</t>
-  </si>
-  <si>
-    <t>Peyton Krebs</t>
-  </si>
-  <si>
-    <t>Ryan McLeod</t>
-  </si>
-  <si>
-    <t>Jacob Bryson</t>
-  </si>
-  <si>
-    <t>Bowen Byram</t>
-  </si>
-  <si>
-    <t>Zach Metsa</t>
-  </si>
-  <si>
-    <t>Owen Power</t>
-  </si>
-  <si>
     <t>Jack Quinn</t>
-  </si>
-  <si>
-    <t>Noah Ostlund</t>
-  </si>
-  <si>
-    <t>Jordan Greenway</t>
-  </si>
-  <si>
-    <t>Josh Dunne</t>
-  </si>
-  <si>
-    <t>Beck Malenstyn</t>
   </si>
 </sst>
 </file>
@@ -529,7 +529,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17a6e381-f7a1-4741-8ddd-fa813da391b1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6a4ee634-f2ad-43ea-a71d-c45df7ff051e}">
   <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
@@ -551,13 +551,13 @@
     </row>
     <row r="2" spans="1:3" ht="12.75">
       <c r="A2" s="1">
-        <v>46025</v>
+        <v>46032</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>190.42</v>
+        <v>200.7395</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="12.75">
@@ -565,7 +565,7 @@
         <v>4</v>
       </c>
       <c r="C3" s="2">
-        <v>182.019</v>
+        <v>192.7394</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="12.75">
@@ -573,7 +573,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="2">
-        <v>178.6441</v>
+        <v>191.0627</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="12.75">
@@ -581,7 +581,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="2">
-        <v>170.9427</v>
+        <v>184.707</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="12.75">
@@ -589,7 +589,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="2">
-        <v>170.8984</v>
+        <v>181.2975</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="12.75">
@@ -597,7 +597,7 @@
         <v>8</v>
       </c>
       <c r="C7" s="2">
-        <v>169.0955</v>
+        <v>180.1376</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="12.75">
@@ -605,7 +605,7 @@
         <v>9</v>
       </c>
       <c r="C8" s="2">
-        <v>164.49</v>
+        <v>174.0069</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="12.75">
@@ -613,7 +613,7 @@
         <v>10</v>
       </c>
       <c r="C9" s="2">
-        <v>163.1335</v>
+        <v>173.7261</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="12.75">
@@ -621,7 +621,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="2">
-        <v>162.2839</v>
+        <v>173.6285</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="12.75">
@@ -629,7 +629,7 @@
         <v>12</v>
       </c>
       <c r="C11" s="2">
-        <v>161.1147</v>
+        <v>169.2165</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="12.75">
@@ -637,7 +637,7 @@
         <v>13</v>
       </c>
       <c r="C12" s="2">
-        <v>158.3171</v>
+        <v>167.7949</v>
       </c>
     </row>
     <row r="13" spans="2:3" ht="12.75">
@@ -645,7 +645,7 @@
         <v>14</v>
       </c>
       <c r="C13" s="2">
-        <v>155.0895</v>
+        <v>164.6102</v>
       </c>
     </row>
     <row r="14" spans="2:3" ht="12.75">
@@ -653,7 +653,7 @@
         <v>15</v>
       </c>
       <c r="C14" s="2">
-        <v>147.5169</v>
+        <v>162.8205</v>
       </c>
     </row>
     <row r="15" spans="2:3" ht="12.75">
@@ -661,7 +661,7 @@
         <v>16</v>
       </c>
       <c r="C15" s="2">
-        <v>147.1174</v>
+        <v>161.9978</v>
       </c>
     </row>
     <row r="16" spans="2:3" ht="12.75">
@@ -669,7 +669,7 @@
         <v>17</v>
       </c>
       <c r="C16" s="2">
-        <v>146.0312</v>
+        <v>158.9038</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="12.75">
@@ -677,7 +677,7 @@
         <v>18</v>
       </c>
       <c r="C17" s="2">
-        <v>141.6688</v>
+        <v>153.8349</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="12.75">
@@ -685,7 +685,7 @@
         <v>19</v>
       </c>
       <c r="C18" s="2">
-        <v>122.9039</v>
+        <v>150.8576</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="12.75">
@@ -693,7 +693,7 @@
         <v>20</v>
       </c>
       <c r="C19" s="2">
-        <v>122.693</v>
+        <v>134.923</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="12.75">
@@ -701,7 +701,7 @@
         <v>21</v>
       </c>
       <c r="C20" s="2">
-        <v>109.9937</v>
+        <v>131.2861</v>
       </c>
     </row>
   </sheetData>
